--- a/docassemble/MAEvictionDefense/data/sources/eviction_vi.xlsx
+++ b/docassemble/MAEvictionDefense/data/sources/eviction_vi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1220"/>
+  <dimension ref="A1:H1224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>06affba7ad2203d850a91c6af6819f61</t>
+          <t>575ad08957cfe9bd85d7f94d8711ed35</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -18207,7 +18207,7 @@
           <t xml:space="preserve">You can continue this interview on another device, or share it with 
 someone who will help you finish it. Choose any of the options below to share
 the interview.
-Right-click and copy [this link](${interview_url()}).
+Right-click and copy [the link to your interview](${interview_url()}).
 % if device() and not device().is_mobile:
 Use your phone's camera to point at this barcode. Click the link that appears
 in the camera's viewfinder.
@@ -18221,7 +18221,7 @@
       <c r="H421" t="inlineStr">
         <is>
           <t xml:space="preserve">Quý vị có thể tiếp tục bài phỏng vấn này trên một thiết bị khác hoặc nhờ người khác giúp quý vị hoàn thành. Hãy chọn bất kỳ tùy chọn nào bên dưới để chia sẻ bài phỏng vấn.
-Nhấp chuột phải rồi sao chép [liên kết này](${interview_url()}).
+Nhấp chuột phải rồi sao chép [liên kết đến bài phỏng vấn của quý vị](${interview_url()}).
 % if device() and not device().is_mobile:
 Hướng máy ảnh điện thoại vào mã vạch này. Nhấp vào liên kết xuất hiện
 trong ống ngắm của máy ảnh.
@@ -40395,7 +40395,7 @@
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>405a7c1de4db0b51f49baacb5de85580</t>
+          <t>8d80904edef43f2eedc35a288289b349</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -40425,7 +40425,7 @@
   ${landlord.name}.
 % endif
 You also need to send a copy of the motion to ${court}.
-Learn more and continue the form online [here](${interview_url()}) or download
+Learn more and [continue the form online](${interview_url()}) or download
 the PDF here: https://gbls.org/tactics/compel.
 </t>
         </is>
@@ -40445,7 +40445,7 @@
   ${landlord.name}.
 % endif
 Quý vị cũng có thể gửi một bản sao đơn thỉnh nguyện tới ${court}.
-Tìm hiểu thêm và tiếp tục với mẫu trực tuyến [tại đây](${interview_url()}) hoặc tải xuống file PDF tại đây: https://gbls.org/tactics/compel.
+Tìm hiểu thêm và [tiếp tục với mẫu trực tuyến](${interview_url()}) hoặc tải xuống file PDF tại đây: https://gbls.org/tactics/compel.
 </t>
         </is>
       </c>
@@ -40722,7 +40722,7 @@
       </c>
       <c r="D955" t="inlineStr">
         <is>
-          <t>26fd8aed4ec30f78c45f916032146cd5</t>
+          <t>cec6553a0281b8bd2f9e4a1f35f60906</t>
         </is>
       </c>
       <c r="E955" t="inlineStr">
@@ -40739,7 +40739,7 @@
         <is>
           <t xml:space="preserve">Someone who was completing an interview using Massachusetts Defense for
 Eviction (MADE) sent you this link.
-Click [here](${interview_url()}) to keep working on the interview.
+[Keep working on the interview](${interview_url()}).
 </t>
         </is>
       </c>
@@ -40747,7 +40747,7 @@
         <is>
           <t xml:space="preserve">Có người đang hoàn tất bài phỏng vấn bằng cách sử dụng công cụ Massachusetts Defense for
 trục xuất (MADE) đã gửi liên kết này cho quý vị.
-Nhấp [vào đây](${interview_url()}) để tiếp tục thực hiện bài phỏng vấn.
+[Tiếp tục thực hiện bài phỏng vấn](${interview_url()}).
 </t>
         </is>
       </c>
@@ -52965,6 +52965,208 @@
         </is>
       </c>
     </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1221" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>a2beb488f5408ec32ba0f33f24c6c5e1</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>By hand</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>Giao tận tay</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1222" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>dfc27ef27b631b0e7114573a439c3180</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>By email</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>Qua email</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1223" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>409b1ef3ad4fe98ad063fb3026c6b250</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>By mail</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>Qua bưu điện</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1224" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>966afd80841437ca4adfcf8f54bfab2a</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You must give a copy of the forms we are working on to your landlord or their 
+attorney. 
+% if case.hearing_date_assigned:
+They need to _get_ the forms no later than 
+**${format_date(case.answer_date)}**.
+% if answer_date_is_holiday:
+Because ${case.answer_date} is ${answer_date_holiday}, you can
+deliver it the next weekday after ${answer_date_holiday}.
+% endif
+% else:
+Give a copy to your landlord or their attorney as soon as you can.
+% endif
+Deliver it in person
+if you can. If your landlord has a lawyer, you can email it to the lawyer.
+If your landlord does not have a lawyer, ask them first before you email it. 
+% if format_date(case.answer_date) == format_date(today()):
+It's too late to mail the paperwork.
+% else:
+Only mail it if you know
+your landlord will get it on or before ${format_date(case.answer_date)}.
+% endif
+</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quý vị phải đưa một bản sao các mẫu đơn mà chúng ta đang soạn cho chủ nhà của quý vị hoặc cho 
+luật sư của họ. 
+% if case.hearing_date_assigned:
+Họ phải _nhận được_ các mẫu đơn chậm nhất là 
+**${format_date(case.answer_date)}**.
+% if answer_date_is_holiday:
+Vì ${case.answer_date} là ${answer_date_holiday}, quý vị có thể
+giao vào ngày làm việc kế tiếp sau ${answer_date_holiday}.
+% endif
+% else:
+Hãy đưa một bản sao cho chủ nhà của quý vị hoặc cho luật sư của họ càng sớm càng tốt.
+% endif
+Hãy giao trực tiếp
+nếu quý vị có thể. Nếu chủ nhà của quý vị có luật sư, quý vị có thể gửi email cho luật sư đó.
+Nếu chủ nhà của quý vị không có luật sư, hãy xin phép họ trước khi gửi email. 
+% if format_date(case.answer_date) == format_date(today()):
+Đã quá muộn để gửi giấy tờ qua bưu điện.
+% else:
+Chỉ gửi qua bưu điện nếu quý vị biết chắc
+chủ nhà sẽ nhận được vào hoặc trước ngày ${format_date(case.answer_date)}.
+% endif
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
